--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24523501-88AC-4A73-93A0-A6F46F0CD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62730695-695D-40EC-942A-59DACE7F7E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3285" yWindow="3285" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="537" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="538" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4659,11 +4667,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="538">
+  <cellXfs count="539">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4679,10 +4688,10 @@
     <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="518" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="516" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="515" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="514" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="513" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4942,9 +4951,9 @@
     <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="257" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="256" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="255" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="254" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="253" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6116,6 +6125,9 @@
       <c r="W14" s="474">
         <v>4</v>
       </c>
+      <c r="X14" s="538">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62730695-695D-40EC-942A-59DACE7F7E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842885E6-7A98-4400-9B71-E931CAD1F46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3285" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="538" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="539" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4667,11 +4675,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="539">
+  <cellXfs count="540">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4687,10 +4696,10 @@
     <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="518" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="516" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="515" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="514" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4950,9 +4959,9 @@
     <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="257" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="256" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="255" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="254" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6184,6 +6193,9 @@
       <c r="W15" s="475">
         <v>3</v>
       </c>
+      <c r="X15" s="539">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842885E6-7A98-4400-9B71-E931CAD1F46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DBB447-9836-48B4-88B7-9A34FBC4A906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6267,6 +6267,9 @@
       <c r="W16" s="5">
         <v>3</v>
       </c>
+      <c r="X16" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DBB447-9836-48B4-88B7-9A34FBC4A906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFAAAC3-6433-4123-9EE9-F1F542E7D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="4320" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="539" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="540" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4675,11 +4683,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="540">
+  <cellXfs count="541">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4695,10 +4704,10 @@
     <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="518" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="516" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="515" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4958,9 +4967,9 @@
     <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="257" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="256" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="255" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6271,7 +6280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
@@ -6341,8 +6350,11 @@
       <c r="W17" s="476">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X17" s="540">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>51</v>
       </c>
@@ -6386,7 +6398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
@@ -6406,7 +6418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -6426,7 +6438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>73</v>
       </c>
@@ -6446,7 +6458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>94</v>
       </c>
@@ -6466,7 +6478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -6522,7 +6534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
@@ -6578,7 +6590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
@@ -6647,7 +6659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>34</v>
       </c>
@@ -6716,7 +6728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
@@ -6787,7 +6799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>95</v>
       </c>
@@ -6811,7 +6823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
@@ -6882,7 +6894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>21</v>
       </c>
@@ -6953,7 +6965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>96</v>
       </c>
@@ -6977,7 +6989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFAAAC3-6433-4123-9EE9-F1F542E7D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FAFCB5-BF21-45DA-A7C6-07FE93964CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="4320" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4665" yWindow="4665" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="540" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="541" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4683,11 +4691,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="541">
+  <cellXfs count="542">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4703,10 +4712,10 @@
     <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="518" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="516" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4966,9 +4975,9 @@
     <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="257" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="256" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6397,6 +6406,9 @@
       <c r="W18" s="477">
         <v>3</v>
       </c>
+      <c r="X18" s="541">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FAFCB5-BF21-45DA-A7C6-07FE93964CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6F1E55-9D54-4D9D-B8CF-57608C46BCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4665" yWindow="4665" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5010" yWindow="5010" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="541" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="542" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4691,11 +4699,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="542">
+  <cellXfs count="543">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4711,10 +4720,10 @@
     <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="518" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="517" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4974,9 +4983,9 @@
     <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="257" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6429,6 +6438,9 @@
       <c r="W19" s="478">
         <v>3</v>
       </c>
+      <c r="X19" s="542">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6F1E55-9D54-4D9D-B8CF-57608C46BCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722D9019-DB76-4FD1-80AB-C1C37CA9836B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="5010" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="5355" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="542" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="543" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4699,11 +4707,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="543">
+  <cellXfs count="544">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4719,10 +4728,10 @@
     <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="518" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4982,9 +4991,9 @@
     <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="258" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6461,6 +6470,9 @@
       <c r="W20" s="479">
         <v>2</v>
       </c>
+      <c r="X20" s="543">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722D9019-DB76-4FD1-80AB-C1C37CA9836B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B2EA96-33A3-4C5B-91FB-B49524B2366E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="5355" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="5700" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="543" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="544" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4707,11 +4715,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="544">
+  <cellXfs count="545">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4727,10 +4736,10 @@
     <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="519" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4990,9 +4999,9 @@
     <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="259" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6493,6 +6502,9 @@
       <c r="W21" s="480">
         <v>4</v>
       </c>
+      <c r="X21" s="544">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B2EA96-33A3-4C5B-91FB-B49524B2366E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D77F77-1BC6-498F-9283-2D99896154B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="5700" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6045" yWindow="6045" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="544" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="545" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4715,11 +4723,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="545">
+  <cellXfs count="546">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4735,10 +4744,10 @@
     <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="520" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4998,9 +5007,9 @@
     <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="260" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6525,6 +6534,9 @@
       <c r="W22" s="481">
         <v>3</v>
       </c>
+      <c r="X22" s="545">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D77F77-1BC6-498F-9283-2D99896154B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DCE3A7-C70C-430C-8DC8-584AA9B32374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6045" yWindow="6045" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6593,6 +6593,9 @@
       <c r="W23" s="4">
         <v>4</v>
       </c>
+      <c r="X23" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DCE3A7-C70C-430C-8DC8-584AA9B32374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8525D42F-BA09-4AF6-807D-863F3F90AD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="545" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="546" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4723,11 +4731,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="546">
+  <cellXfs count="547">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4743,10 +4752,10 @@
     <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="521" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5006,9 +5015,9 @@
     <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="261" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6652,6 +6661,9 @@
       <c r="W24" s="482">
         <v>5</v>
       </c>
+      <c r="X24" s="546">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8525D42F-BA09-4AF6-807D-863F3F90AD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BF42AB-5B27-4699-9B56-0E8B4D7F784A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="546" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="547" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4731,11 +4739,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="547">
+  <cellXfs count="548">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4751,10 +4760,10 @@
     <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="522" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5014,9 +5023,9 @@
     <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="262" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6733,6 +6742,9 @@
       <c r="W25" s="483">
         <v>2</v>
       </c>
+      <c r="X25" s="547">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BF42AB-5B27-4699-9B56-0E8B4D7F784A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F947B9-9C02-441D-A92E-374017DB948A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2535" yWindow="2550" windowWidth="5100" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="547" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="548" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4739,11 +4747,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="548">
+  <cellXfs count="549">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4759,10 +4768,10 @@
     <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="523" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5022,9 +5031,9 @@
     <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="263" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6814,6 +6823,9 @@
       <c r="W26" s="484">
         <v>5</v>
       </c>
+      <c r="X26" s="548">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F947B9-9C02-441D-A92E-374017DB948A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF0B1EF-3022-465B-A444-119EE75F5787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2535" yWindow="2550" windowWidth="5100" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="6210" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="548" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="549" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4747,11 +4755,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="549">
+  <cellXfs count="550">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4767,10 +4776,10 @@
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="524" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5030,9 +5039,9 @@
     <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="264" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6921,6 +6930,9 @@
       <c r="W28" s="486">
         <v>3</v>
       </c>
+      <c r="X28" s="549">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF0B1EF-3022-465B-A444-119EE75F5787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBA8756-6495-4CA2-8A9C-189A9A2A8883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="6210" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="2550" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="549" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="550" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4755,11 +4763,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="550">
+  <cellXfs count="551">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4775,10 +4784,10 @@
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="525" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5038,9 +5047,9 @@
     <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="265" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7004,6 +7013,9 @@
       <c r="W29" s="487">
         <v>5</v>
       </c>
+      <c r="X29" s="550">
+        <v>5</v>
+      </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBA8756-6495-4CA2-8A9C-189A9A2A8883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C863DF4A-7E9A-4D32-9327-9EFC64E58C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2550" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="2895" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="550" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="551" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4763,11 +4771,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="551">
+  <cellXfs count="552">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4783,10 +4792,10 @@
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="526" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5046,9 +5055,9 @@
     <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="266" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7087,6 +7096,9 @@
       <c r="W30" s="488">
         <v>2</v>
       </c>
+      <c r="X30" s="551">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C863DF4A-7E9A-4D32-9327-9EFC64E58C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF5F39B-FC3F-4B90-AFA8-1A2E65798DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2895" yWindow="2895" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="551" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="552" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4771,11 +4779,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="552">
+  <cellXfs count="553">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4791,10 +4800,10 @@
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="527" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5054,9 +5063,9 @@
     <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="267" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7123,6 +7132,9 @@
       <c r="W31" s="489">
         <v>5</v>
       </c>
+      <c r="X31" s="552">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF5F39B-FC3F-4B90-AFA8-1A2E65798DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABE7C8C-52D8-42AE-9050-4C553DADCE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="2895" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="552" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="553" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4779,11 +4787,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="553">
+  <cellXfs count="554">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4799,10 +4808,10 @@
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="528" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5062,9 +5071,9 @@
     <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="268" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7206,6 +7215,9 @@
       <c r="W32" s="490">
         <v>3</v>
       </c>
+      <c r="X32" s="553">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABE7C8C-52D8-42AE-9050-4C553DADCE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6473091-D59C-49CB-9DF9-61F81940F858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="553" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="554" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4787,11 +4795,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="554">
+  <cellXfs count="555">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4807,10 +4816,10 @@
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="529" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5070,9 +5079,9 @@
     <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="269" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7219,7 +7228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>14</v>
       </c>
@@ -7289,8 +7298,11 @@
       <c r="W33" s="491">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" s="554">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
@@ -7361,7 +7373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>97</v>
       </c>
@@ -7385,7 +7397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>99</v>
       </c>
@@ -7409,7 +7421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>100</v>
       </c>
@@ -7433,7 +7445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>101</v>
       </c>
@@ -7457,7 +7469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>102</v>
       </c>
@@ -7481,7 +7493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -7552,7 +7564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>52</v>
       </c>
@@ -7596,7 +7608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>9</v>
       </c>
@@ -7667,7 +7679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>48</v>
       </c>
@@ -7717,7 +7729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>17</v>
       </c>
@@ -7788,7 +7800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>47</v>
       </c>
@@ -7838,7 +7850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>37</v>
       </c>
@@ -7897,7 +7909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -7968,7 +7980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>19</v>
       </c>

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6473091-D59C-49CB-9DF9-61F81940F858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43294BC3-245F-42E8-A46E-7E502217857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="554" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="555" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4795,11 +4803,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="555">
+  <cellXfs count="556">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4815,10 +4824,10 @@
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5078,9 +5087,9 @@
     <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="270" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7372,6 +7381,9 @@
       <c r="W34" s="492">
         <v>3</v>
       </c>
+      <c r="X34" s="555">
+        <v>3</v>
+      </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43294BC3-245F-42E8-A46E-7E502217857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE87395-2C7C-4A72-8332-C5CFC65E91FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3930" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="4275" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="555" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="556" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4803,11 +4811,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="556">
+  <cellXfs count="557">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4823,10 +4832,10 @@
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5086,9 +5095,9 @@
     <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="271" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7408,6 +7417,9 @@
       <c r="W35" s="493">
         <v>3</v>
       </c>
+      <c r="X35" s="556">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE87395-2C7C-4A72-8332-C5CFC65E91FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407C54D7-5A44-426A-AAC3-CEFBCA1A0652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="4275" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="4620" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="556" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="557" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4811,11 +4819,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="557">
+  <cellXfs count="558">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4831,10 +4840,10 @@
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5094,9 +5103,9 @@
     <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="272" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7444,6 +7453,9 @@
       <c r="W36" s="494">
         <v>2</v>
       </c>
+      <c r="X36" s="557">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407C54D7-5A44-426A-AAC3-CEFBCA1A0652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8828128B-5B5F-4B2E-9731-6F7F76880F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="4620" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4965" yWindow="4965" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="557" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="558" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4819,11 +4827,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="558">
+  <cellXfs count="559">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4839,10 +4848,10 @@
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5102,9 +5111,9 @@
     <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="273" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7480,6 +7489,9 @@
       <c r="W37" s="495">
         <v>4</v>
       </c>
+      <c r="X37" s="558">
+        <v>2</v>
+      </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8828128B-5B5F-4B2E-9731-6F7F76880F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1510A407-9829-4367-89E7-E60F169D8996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4965" yWindow="4965" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5310" yWindow="5310" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="558" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="559" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4827,11 +4835,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="559">
+  <cellXfs count="560">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4847,10 +4856,10 @@
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5110,9 +5119,9 @@
     <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="274" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7516,6 +7525,9 @@
       <c r="W38" s="496">
         <v>3</v>
       </c>
+      <c r="X38" s="559">
+        <v>3</v>
+      </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1510A407-9829-4367-89E7-E60F169D8996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793A7D57-85CC-43F3-A3D7-BC743F8F022C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="5310" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5655" yWindow="5655" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="559" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="560" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4835,11 +4843,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="560">
+  <cellXfs count="561">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4855,10 +4864,10 @@
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5118,9 +5127,9 @@
     <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="275" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7552,6 +7561,9 @@
       <c r="W39" s="497">
         <v>2</v>
       </c>
+      <c r="X39" s="560">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793A7D57-85CC-43F3-A3D7-BC743F8F022C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31F35C5-0C98-4C88-868A-0CD67701784A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="5655" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6000" yWindow="6000" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="560" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="561" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4843,11 +4851,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="561">
+  <cellXfs count="562">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4863,10 +4872,10 @@
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5126,9 +5135,9 @@
     <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="276" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7635,6 +7644,9 @@
       <c r="W40" s="498">
         <v>4</v>
       </c>
+      <c r="X40" s="561">
+        <v>4</v>
+      </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31F35C5-0C98-4C88-868A-0CD67701784A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5EB688-D4E7-42C1-9ACC-E0A2540CCD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="6000" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="561" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="562" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4851,11 +4859,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="562">
+  <cellXfs count="563">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4871,10 +4880,10 @@
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5134,9 +5143,9 @@
     <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="277" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7691,6 +7700,9 @@
       <c r="W41" s="499">
         <v>3</v>
       </c>
+      <c r="X41" s="562">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5EB688-D4E7-42C1-9ACC-E0A2540CCD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB81462-FA82-4B6F-83BF-FB3B453ACCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="562" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="563" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4859,11 +4867,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="563">
+  <cellXfs count="564">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4879,10 +4888,10 @@
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5142,9 +5151,9 @@
     <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="278" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7774,6 +7783,9 @@
       <c r="W42" s="500">
         <v>2</v>
       </c>
+      <c r="X42" s="563">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB81462-FA82-4B6F-83BF-FB3B453ACCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32FC85C-A571-49CE-9889-990B8A2144BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="563" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="564" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4867,11 +4875,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="564">
+  <cellXfs count="565">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4887,10 +4896,10 @@
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5150,9 +5159,9 @@
     <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="279" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7836,6 +7845,9 @@
       <c r="W43" s="501">
         <v>2</v>
       </c>
+      <c r="X43" s="564">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32FC85C-A571-49CE-9889-990B8A2144BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D6A8A2-62D3-468E-B346-659576E00B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="3030" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="564" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="565" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4875,11 +4883,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="565">
+  <cellXfs count="566">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4895,10 +4904,10 @@
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5158,9 +5167,9 @@
     <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="280" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7919,6 +7928,9 @@
       <c r="W44" s="502">
         <v>4</v>
       </c>
+      <c r="X44" s="565">
+        <v>3</v>
+      </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D6A8A2-62D3-468E-B346-659576E00B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055B1116-2748-4023-9AD0-6B76521B196B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3375" yWindow="3375" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="565" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="566" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4883,11 +4891,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="566">
+  <cellXfs count="567">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4903,10 +4912,10 @@
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5166,9 +5175,9 @@
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="281" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7981,6 +7990,9 @@
       <c r="W45" s="503">
         <v>4</v>
       </c>
+      <c r="X45" s="566">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055B1116-2748-4023-9AD0-6B76521B196B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE329229-0B89-4F5C-BCA0-B92D21A356EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="3375" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="566" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="567" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4891,11 +4899,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="567">
+  <cellXfs count="568">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4911,10 +4920,10 @@
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5174,9 +5183,9 @@
     <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="282" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8052,6 +8061,9 @@
       <c r="W46" s="504">
         <v>4</v>
       </c>
+      <c r="X46" s="567">
+        <v>3</v>
+      </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE329229-0B89-4F5C-BCA0-B92D21A356EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90CD02B-0CD1-4DC8-9F06-A1D9647DE953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3720" yWindow="3720" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="567" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="568" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4899,11 +4907,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="568">
+  <cellXfs count="569">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4919,10 +4928,10 @@
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5182,9 +5191,9 @@
     <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="283" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8135,6 +8144,9 @@
       <c r="W47" s="505">
         <v>4</v>
       </c>
+      <c r="X47" s="568">
+        <v>3</v>
+      </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90CD02B-0CD1-4DC8-9F06-A1D9647DE953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58957609-AE7D-446A-84E2-CC9D2483F380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3720" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4065" yWindow="4065" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="568" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="569" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4907,11 +4915,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="569">
+  <cellXfs count="570">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4927,10 +4936,10 @@
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5190,9 +5199,9 @@
     <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="284" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8218,6 +8227,9 @@
       <c r="W48" s="506">
         <v>4</v>
       </c>
+      <c r="X48" s="569">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58957609-AE7D-446A-84E2-CC9D2483F380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9058DA6-13DC-4481-8D17-6B84B376EA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4065" yWindow="4065" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4410" yWindow="4410" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="569" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="570" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4915,11 +4923,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="570">
+  <cellXfs count="571">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4935,10 +4944,10 @@
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="545" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5198,9 +5207,9 @@
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="285" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8231,7 +8240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>27</v>
       </c>
@@ -8301,8 +8310,11 @@
       <c r="W49" s="507">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X49" s="570">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>103</v>
       </c>
@@ -8326,7 +8338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1</v>
       </c>
@@ -8397,7 +8409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>10</v>
       </c>
@@ -8468,7 +8480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>24</v>
       </c>
@@ -8539,7 +8551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>18</v>
       </c>
@@ -8610,7 +8622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>31</v>
       </c>
@@ -8681,7 +8693,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>12</v>
       </c>
@@ -8752,7 +8764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
         <v>28</v>
       </c>
@@ -8823,7 +8835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>22</v>
       </c>
@@ -8894,7 +8906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>45</v>
       </c>
@@ -8944,7 +8956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -9015,7 +9027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>25</v>
       </c>
@@ -9086,7 +9098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>26</v>
       </c>
@@ -9157,7 +9169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>11</v>
       </c>
@@ -9228,7 +9240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>16</v>
       </c>

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9058DA6-13DC-4481-8D17-6B84B376EA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11D4868-2399-44E5-A21B-C9D572C33265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="4410" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4755" yWindow="4755" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="570" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="571" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4923,11 +4931,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="571">
+  <cellXfs count="572">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4943,10 +4952,10 @@
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="546" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5206,9 +5215,9 @@
     <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="286" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8337,6 +8346,9 @@
       <c r="W50" s="508">
         <v>5</v>
       </c>
+      <c r="X50" s="571">
+        <v>3</v>
+      </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11D4868-2399-44E5-A21B-C9D572C33265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32A99BE-835B-4EB4-8C61-5469048DA2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="4755" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="5100" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="571" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="572" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4931,11 +4939,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="572">
+  <cellXfs count="573">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4951,10 +4960,10 @@
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="547" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5214,9 +5223,9 @@
     <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8420,6 +8429,9 @@
       <c r="W51" s="509">
         <v>4</v>
       </c>
+      <c r="X51" s="572">
+        <v>4</v>
+      </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32A99BE-835B-4EB4-8C61-5469048DA2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD368B5-3C6F-4565-B2AB-8861B304860A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="5100" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5445" yWindow="5445" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="572" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="573" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4939,11 +4947,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="573">
+  <cellXfs count="574">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4959,10 +4968,10 @@
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="548" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5222,9 +5231,9 @@
     <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="288" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8503,6 +8512,9 @@
       <c r="W52" s="510">
         <v>3</v>
       </c>
+      <c r="X52" s="573">
+        <v>3</v>
+      </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD368B5-3C6F-4565-B2AB-8861B304860A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2AB887-64FE-4F1D-BD65-DC0EBDA9F3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5445" yWindow="5445" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5790" yWindow="5790" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="573" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="574" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4947,11 +4955,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="574">
+  <cellXfs count="575">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4967,10 +4976,10 @@
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="549" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5230,9 +5239,9 @@
     <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="289" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8586,6 +8595,9 @@
       <c r="W53" s="511">
         <v>4</v>
       </c>
+      <c r="X53" s="574">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2AB887-64FE-4F1D-BD65-DC0EBDA9F3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDFBDB1-B35B-4288-B385-1D409AD84F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="5790" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6135" yWindow="6135" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="574" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="575" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4955,11 +4963,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="575">
+  <cellXfs count="576">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="566" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4975,10 +4984,10 @@
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="550" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5238,9 +5247,9 @@
     <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="290" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8669,6 +8678,9 @@
       <c r="W54" s="512">
         <v>4</v>
       </c>
+      <c r="X54" s="575">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDFBDB1-B35B-4288-B385-1D409AD84F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72987D7C-CED2-47CF-B254-C9EC462E07D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6135" yWindow="6135" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="575" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="576" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4963,11 +4971,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="576">
+  <cellXfs count="577">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="567" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4983,10 +4992,10 @@
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="551" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5246,9 +5255,9 @@
     <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8752,6 +8761,9 @@
       <c r="W55" s="513">
         <v>4</v>
       </c>
+      <c r="X55" s="576">
+        <v>5</v>
+      </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72987D7C-CED2-47CF-B254-C9EC462E07D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C35635-F866-4B18-A89C-59ABD5C44388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="576" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="577" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4971,11 +4979,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="577">
+  <cellXfs count="578">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="568" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4991,10 +5000,10 @@
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="552" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5254,9 +5263,9 @@
     <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="292" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8835,6 +8844,9 @@
       <c r="W56" s="514">
         <v>4</v>
       </c>
+      <c r="X56" s="577">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C35635-F866-4B18-A89C-59ABD5C44388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA958304-F6EB-4AD5-8179-DBD9B2B97B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="577" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="578" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4979,11 +4987,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="578">
+  <cellXfs count="579">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="569" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4999,10 +5008,10 @@
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="553" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5262,9 +5271,9 @@
     <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="293" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8918,6 +8927,9 @@
       <c r="W57" s="515">
         <v>1</v>
       </c>
+      <c r="X57" s="578">
+        <v>3</v>
+      </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA958304-F6EB-4AD5-8179-DBD9B2B97B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727A9769-C67F-47DF-B460-C10AA7872224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="578" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="579" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4987,11 +4995,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="579">
+  <cellXfs count="580">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="570" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5007,10 +5016,10 @@
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="554" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5270,9 +5279,9 @@
     <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="294" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9001,6 +9010,9 @@
       <c r="W58" s="516">
         <v>4</v>
       </c>
+      <c r="X58" s="579">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727A9769-C67F-47DF-B460-C10AA7872224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E2C72F-ED61-4BCB-9210-B6AC1A64ECFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="579" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="580" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4995,11 +5003,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="580">
+  <cellXfs count="581">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="571" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5015,10 +5024,10 @@
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="555" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5278,9 +5287,9 @@
     <xf numFmtId="0" fontId="301" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="295" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9063,6 +9072,9 @@
       <c r="W59" s="517">
         <v>4</v>
       </c>
+      <c r="X59" s="580">
+        <v>5</v>
+      </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E2C72F-ED61-4BCB-9210-B6AC1A64ECFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CBD34D-FCAE-45C4-A8D5-80B535B0AFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3285" yWindow="3285" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="580" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="581" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5003,11 +5011,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="581">
+  <cellXfs count="582">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="572" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5023,10 +5032,10 @@
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5286,9 +5295,9 @@
     <xf numFmtId="0" fontId="302" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="301" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="296" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9146,6 +9155,9 @@
       <c r="W60" s="518">
         <v>4</v>
       </c>
+      <c r="X60" s="581">
+        <v>5</v>
+      </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CBD34D-FCAE-45C4-A8D5-80B535B0AFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE697E2-2FDB-4BB1-A709-5BFD015F0E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3285" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="581" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="582" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5011,11 +5019,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="582">
+  <cellXfs count="583">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="573" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5031,10 +5040,10 @@
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="557" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5294,9 +5303,9 @@
     <xf numFmtId="0" fontId="303" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="302" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="301" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="297" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9229,6 +9238,9 @@
       <c r="W61" s="519">
         <v>5</v>
       </c>
+      <c r="X61" s="582">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE697E2-2FDB-4BB1-A709-5BFD015F0E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ED0C97-31D5-40C2-88C0-C7703D4AA83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="582" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="583" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5019,11 +5027,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="583">
+  <cellXfs count="584">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="574" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5039,10 +5048,10 @@
     <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="558" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5302,9 +5311,9 @@
     <xf numFmtId="0" fontId="304" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="303" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="302" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="301" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="581" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="298" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9312,6 +9321,9 @@
       <c r="W62" s="520">
         <v>3</v>
       </c>
+      <c r="X62" s="583">
+        <v>5</v>
+      </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">

--- a/datacamp.xlsx
+++ b/datacamp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ED0C97-31D5-40C2-88C0-C7703D4AA83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B138CC37-8BE2-443C-90DB-4A88582AF6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="4320" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,12 +343,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="583" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="584" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5027,11 +5035,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="584">
+  <cellXfs count="585">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="579" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="578" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="577" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="576" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="575" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5047,10 +5056,10 @@
     <xf numFmtId="0" fontId="565" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="564" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="563" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="561" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="560" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5310,9 +5319,9 @@
     <xf numFmtId="0" fontId="305" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="304" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="303" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="302" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="581" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="582" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="301" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="300" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="299" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9395,6 +9404,9 @@
       <c r="W63" s="521">
         <v>1</v>
       </c>
+      <c r="X63" s="584">
+        <v>5</v>
+      </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
